--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/kyriba_rollout_risks_defects.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/kyriba_rollout_risks_defects.xlsx
@@ -485,22 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Change mgmt</t>
+          <t>Connectivity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connectivity</t>
+          <t>Change mgmt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Data mapping</t>
+          <t>Change mgmt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>JPMorgan</t>
         </is>
       </c>
     </row>
@@ -593,22 +593,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Change mgmt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
     </row>
@@ -620,22 +620,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Change mgmt</t>
+          <t>Data mapping</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Connectivity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Santander</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Connectivity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
     </row>
@@ -733,17 +733,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Santander</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Change mgmt</t>
+          <t>Connectivity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>DBS</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
@@ -809,22 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Change mgmt</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mitigating</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Standard Chartered</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Santander</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Change mgmt</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
@@ -890,22 +890,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Connectivity</t>
+          <t>Change mgmt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>Citi</t>
         </is>
       </c>
     </row>
@@ -917,22 +917,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>JPMorgan</t>
         </is>
       </c>
     </row>
@@ -944,22 +944,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Change mgmt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Mitigating</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>Standard Chartered</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Change mgmt</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Data mapping</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Connectivity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>DBS</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>HSBC</t>
         </is>
       </c>
     </row>
